--- a/bulkStudent/students.xlsx
+++ b/bulkStudent/students.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="2">
   <si>
     <t>name</t>
   </si>
@@ -348,7 +348,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" customWidth="1"/>
@@ -364,6 +364,151 @@
         <v>1</v>
       </c>
     </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
